--- a/ApiDataBase/AutoGenCode.xlsx
+++ b/ApiDataBase/AutoGenCode.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WorkspaceDDigital\LSM7002MNiosProject\ApiDataBase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BCFA667-367D-4F4D-8987-30D90CAF2463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F1ADE3-DEE8-400C-BB62-835855C8DB70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="bydtatype" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">bydtatype!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">bydtatype!$A$1:$O$105</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="268">
   <si>
     <t>SN</t>
   </si>
@@ -810,11 +810,6 @@
   </si>
   <si>
     <t>LMS7002M_rbb_set_pga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Set the PGA gain for the RX baseband.
-</t>
   </si>
   <si>
     <t>LMS7002M_rfe_set_lna</t>
@@ -1042,6 +1037,24 @@
 Note: there is a size 16 table for every NCO, we are just using entry 0.
 Math: freqHz = freqRel * sampleRate           freqRel --&gt; (0-0.5)
 </t>
+  </si>
+  <si>
+    <t>TuneRxFilter_8051</t>
+  </si>
+  <si>
+    <t>Set the RX baseband filter bandwidth with 8051 MCU.
+The actual bandwidth will be greater than or equal to the requested bandwidth.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Set the PGA gain for the RX baseband. Range[-12, 19]
+</t>
+  </si>
+  <si>
+    <t>CalibrateAll</t>
+  </si>
+  <si>
+    <t>Runs TX and RX calibration on the selected channel using the specified bandwidth.</t>
   </si>
 </sst>
 </file>
@@ -1095,7 +1108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1124,6 +1137,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1320,7 +1336,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T104"/>
+  <dimension ref="A1:T106"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" customWidth="1"/>
@@ -1479,7 +1495,7 @@
         <v>25</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D4" s="1">
         <v>1</v>
@@ -1840,16 +1856,16 @@
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>26</v>
@@ -1858,7 +1874,7 @@
         <v>27</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>29</v>
@@ -1891,10 +1907,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>258</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
@@ -1910,7 +1926,7 @@
         <v>27</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>29</v>
@@ -2710,10 +2726,10 @@
         <v>4</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D30" s="1">
         <v>6</v>
@@ -2729,7 +2745,7 @@
         <v>77</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I30" s="4" t="s">
         <v>29</v>
@@ -2762,10 +2778,10 @@
         <v>5</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D31" s="1">
         <v>6</v>
@@ -2781,7 +2797,7 @@
         <v>77</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I31" s="4" t="s">
         <v>29</v>
@@ -2814,10 +2830,10 @@
         <v>6</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D32" s="1">
         <v>6</v>
@@ -2833,7 +2849,7 @@
         <v>77</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I32" s="4" t="s">
         <v>29</v>
@@ -2866,10 +2882,10 @@
         <v>7</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>253</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>254</v>
       </c>
       <c r="D33" s="1">
         <v>6</v>
@@ -2885,7 +2901,7 @@
         <v>77</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I33" s="4" t="s">
         <v>29</v>
@@ -2918,10 +2934,10 @@
         <v>8</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D34" s="1">
         <v>6</v>
@@ -2937,7 +2953,7 @@
         <v>77</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>29</v>
@@ -3387,7 +3403,7 @@
         <v>103</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D44" s="1">
         <v>8</v>
@@ -3412,7 +3428,7 @@
         <v>73</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>22</v>
@@ -3707,7 +3723,7 @@
         <v>124</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D52" s="1">
         <v>12</v>
@@ -3809,7 +3825,7 @@
         <v>29</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>96</v>
@@ -3818,10 +3834,10 @@
         <v>180</v>
       </c>
       <c r="M54" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="N54" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="N54" s="1" t="s">
-        <v>236</v>
       </c>
       <c r="O54" s="1" t="s">
         <v>54</v>
@@ -4311,7 +4327,7 @@
         <v>153</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D65" s="1">
         <v>15</v>
@@ -4412,10 +4428,10 @@
         <v>9</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D67" s="1">
         <v>15</v>
@@ -4431,7 +4447,7 @@
         <v>140</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I67" s="4" t="s">
         <v>29</v>
@@ -4759,7 +4775,7 @@
         <v>170</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D75" s="1">
         <v>18</v>
@@ -4811,7 +4827,7 @@
         <v>175</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D76" s="1">
         <v>18</v>
@@ -4863,7 +4879,7 @@
         <v>181</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D77" s="1">
         <v>18</v>
@@ -4943,7 +4959,7 @@
         <v>176</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D79" s="1">
         <v>19</v>
@@ -5023,7 +5039,7 @@
         <v>182</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D81" s="1">
         <v>20</v>
@@ -5075,7 +5091,7 @@
         <v>186</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D82" s="1">
         <v>20</v>
@@ -5179,7 +5195,7 @@
         <v>189</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D84" s="1">
         <v>20</v>
@@ -5231,7 +5247,7 @@
         <v>190</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D85" s="1">
         <v>20</v>
@@ -5311,7 +5327,7 @@
         <v>191</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D87" s="1">
         <v>21</v>
@@ -5492,10 +5508,10 @@
         <v>2</v>
       </c>
       <c r="B91" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C91" s="4" t="s">
         <v>260</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>261</v>
       </c>
       <c r="D91" s="1">
         <v>22</v>
@@ -5539,206 +5555,206 @@
         <v>typedef int bb_filer_set_num_calibrate(LMS7002M_t *);</v>
       </c>
     </row>
-    <row r="92" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B92" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C92" s="7"/>
-      <c r="D92" s="7"/>
-      <c r="J92" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K92" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L92" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="M92" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="N92" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="O92" s="7"/>
-      <c r="P92" s="7"/>
-      <c r="Q92"/>
-    </row>
-    <row r="93" spans="1:17" ht="51" x14ac:dyDescent="0.2">
-      <c r="A93" s="1">
-        <v>0</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="D93" s="1">
-        <v>23</v>
-      </c>
-      <c r="E93" s="1" t="str">
-        <f t="shared" ref="E93:E100" si="9">DEC2HEX(_xlfn.BITOR(_xlfn.BITLSHIFT(A93,5),D93))</f>
-        <v>17</v>
-      </c>
-      <c r="F93" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="G93" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="I93" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J93" s="3" t="s">
+    <row r="92" spans="1:17" ht="51" x14ac:dyDescent="0.2">
+      <c r="A92" s="1">
+        <v>3</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="D92" s="1">
+        <v>22</v>
+      </c>
+      <c r="E92" s="1" t="str">
+        <f>DEC2HEX(_xlfn.BITOR(_xlfn.BITLSHIFT(A92,5),D92))</f>
+        <v>76</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="I92" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J92" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="K93" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="L93" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M93" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N93" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O93" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P93" t="str">
-        <f t="shared" ref="P93:P100" si="10">CONCATENATE("typedef ",O93," ",LOWER(F93), "_",  SUBSTITUTE(LOWER(H93), " ", "_"),"(", I93,");")</f>
-        <v>typedef void trf_rbb_rfe_num_frequency_tunning(LMS7002M_t *);</v>
-      </c>
+      <c r="K92" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="M92" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N92" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O92" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P92" t="str">
+        <f>CONCATENATE("typedef ",O92," ",LOWER(F92), "_",  SUBSTITUTE(LOWER(H92), " ", "_"),"(", I92,");")</f>
+        <v>typedef int bb_filer_set_num_calibrate(LMS7002M_t *);</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C93" s="7"/>
+      <c r="D93" s="7"/>
+      <c r="J93" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K93" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L93" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M93" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N93" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="O93" s="7"/>
+      <c r="P93" s="7"/>
+      <c r="Q93"/>
     </row>
     <row r="94" spans="1:17" ht="51" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D94" s="1">
         <v>23</v>
       </c>
       <c r="E94" s="1" t="str">
+        <f t="shared" ref="E94:E102" si="9">DEC2HEX(_xlfn.BITOR(_xlfn.BITLSHIFT(A94,5),D94))</f>
+        <v>17</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I94" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M94" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N94" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O94" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P94" t="str">
+        <f t="shared" ref="P94:P102" si="10">CONCATENATE("typedef ",O94," ",LOWER(F94), "_",  SUBSTITUTE(LOWER(H94), " ", "_"),"(", I94,");")</f>
+        <v>typedef void trf_rbb_rfe_num_frequency_tunning(LMS7002M_t *);</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" ht="51" x14ac:dyDescent="0.2">
+      <c r="A95" s="1">
+        <v>1</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D95" s="1">
+        <v>23</v>
+      </c>
+      <c r="E95" s="1" t="str">
         <f t="shared" si="9"/>
         <v>37</v>
       </c>
-      <c r="F94" s="6" t="s">
+      <c r="F95" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="G94" s="4" t="s">
+      <c r="G95" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="H94" s="1" t="s">
+      <c r="H95" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="I94" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J94" s="3" t="s">
+      <c r="I95" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J95" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="K94" s="1" t="s">
+      <c r="K95" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="L94" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M94" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N94" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O94" s="1" t="s">
+      <c r="L95" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M95" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N95" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O95" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="P94" t="str">
+      <c r="P95" t="str">
         <f t="shared" si="10"/>
         <v>typedef void trf_rbb_rfe_num_frequency_tunning(LMS7002M_t *);</v>
       </c>
     </row>
-    <row r="95" spans="1:17" ht="51" x14ac:dyDescent="0.2">
-      <c r="A95" s="1">
+    <row r="96" spans="1:17" ht="51" x14ac:dyDescent="0.2">
+      <c r="A96" s="1">
         <v>2</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B96" t="s">
         <v>206</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="C96" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="D95" s="1">
+      <c r="D96" s="1">
         <v>23</v>
       </c>
-      <c r="E95" s="1" t="str">
+      <c r="E96" s="1" t="str">
         <f t="shared" si="9"/>
         <v>57</v>
-      </c>
-      <c r="F95" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="I95" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J95" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="K95" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="L95" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M95" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N95" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O95" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="P95" t="str">
-        <f t="shared" si="10"/>
-        <v>typedef double trf_rbb_rfe_num_gain(LMS7002M_t *);</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" ht="51" x14ac:dyDescent="0.2">
-      <c r="A96" s="1">
-        <v>3</v>
-      </c>
-      <c r="B96" t="s">
-        <v>210</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="D96" s="1">
-        <v>23</v>
-      </c>
-      <c r="E96" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>77</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>202</v>
@@ -5775,22 +5791,22 @@
         <v>typedef double trf_rbb_rfe_num_gain(LMS7002M_t *);</v>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:17" ht="51" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B97" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D97" s="1">
         <v>23</v>
       </c>
       <c r="E97" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="F97" s="6" t="s">
         <v>202</v>
@@ -5827,22 +5843,22 @@
         <v>typedef double trf_rbb_rfe_num_gain(LMS7002M_t *);</v>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:17" ht="51" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B98" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>215</v>
+        <v>265</v>
       </c>
       <c r="D98" s="1">
         <v>23</v>
       </c>
       <c r="E98" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>B7</v>
+        <v>97</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>202</v>
@@ -5879,22 +5895,22 @@
         <v>typedef double trf_rbb_rfe_num_gain(LMS7002M_t *);</v>
       </c>
     </row>
-    <row r="99" spans="1:17" ht="51" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B99" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D99" s="1">
         <v>23</v>
       </c>
       <c r="E99" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>D7</v>
+        <v>B7</v>
       </c>
       <c r="F99" s="6" t="s">
         <v>202</v>
@@ -5931,22 +5947,22 @@
         <v>typedef double trf_rbb_rfe_num_gain(LMS7002M_t *);</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:17" ht="51" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B100" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D100" s="1">
         <v>23</v>
       </c>
       <c r="E100" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>F7</v>
+        <v>D7</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>202</v>
@@ -5983,59 +5999,81 @@
         <v>typedef double trf_rbb_rfe_num_gain(LMS7002M_t *);</v>
       </c>
     </row>
-    <row r="101" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B101" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C101" s="7"/>
-      <c r="D101" s="7"/>
-      <c r="J101" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K101" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L101" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="M101" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="N101" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="O101" s="7"/>
-      <c r="P101" s="7"/>
-      <c r="Q101"/>
-    </row>
-    <row r="102" spans="1:17" ht="51" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A101" s="1">
+        <v>7</v>
+      </c>
+      <c r="B101" t="s">
+        <v>217</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D101" s="1">
+        <v>23</v>
+      </c>
+      <c r="E101" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>F7</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="I101" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="L101" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M101" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N101" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O101" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="P101" t="str">
+        <f t="shared" si="10"/>
+        <v>typedef double trf_rbb_rfe_num_gain(LMS7002M_t *);</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
-        <v>0</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>220</v>
+        <v>8</v>
+      </c>
+      <c r="B102" t="s">
+        <v>266</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>221</v>
+        <v>267</v>
       </c>
       <c r="D102" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E102" s="1" t="str">
-        <f>DEC2HEX(_xlfn.BITOR(_xlfn.BITLSHIFT(A102,5),D102))</f>
-        <v>18</v>
+        <f t="shared" si="9"/>
+        <v>117</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="G102" s="4" t="s">
-        <v>223</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="G102" s="4"/>
       <c r="H102" s="1" t="s">
-        <v>224</v>
+        <v>173</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>29</v>
@@ -6044,23 +6082,23 @@
         <v>96</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L102" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M102" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N102" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="L102" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M102" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N102" s="11" t="s">
         <v>22</v>
       </c>
       <c r="O102" s="1" t="s">
-        <v>225</v>
+        <v>30</v>
       </c>
       <c r="P102" t="str">
         <f>CONCATENATE("typedef ",O102," ",LOWER(F102), "_",  SUBSTITUTE(LOWER(H102), " ", "_"),"(", I102,");")</f>
-        <v>typedef uint16_t readrssi_num_rssi(LMS7002M_t *);</v>
+        <v>typedef void trf_rbb_rfe_num_calibrate(LMS7002M_t *);</v>
       </c>
     </row>
     <row r="103" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -6091,16 +6129,96 @@
       <c r="P103" s="7"/>
       <c r="Q103"/>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="E104" s="1"/>
-      <c r="F104" s="6"/>
-      <c r="G104" s="4"/>
-      <c r="H104" s="1"/>
-      <c r="I104" s="4"/>
-      <c r="J104" s="3"/>
+    <row r="104" spans="1:17" ht="51" x14ac:dyDescent="0.2">
+      <c r="A104" s="1">
+        <v>0</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D104" s="1">
+        <v>24</v>
+      </c>
+      <c r="E104" s="1" t="str">
+        <f>DEC2HEX(_xlfn.BITOR(_xlfn.BITLSHIFT(A104,5),D104))</f>
+        <v>18</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="I104" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J104" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L104" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M104" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N104" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O104" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="P104" t="str">
+        <f>CONCATENATE("typedef ",O104," ",LOWER(F104), "_",  SUBSTITUTE(LOWER(H104), " ", "_"),"(", I104,");")</f>
+        <v>typedef uint16_t readrssi_num_rssi(LMS7002M_t *);</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C105" s="7"/>
+      <c r="D105" s="7"/>
+      <c r="J105" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K105" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L105" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M105" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N105" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="O105" s="7"/>
+      <c r="P105" s="7"/>
+      <c r="Q105"/>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="E106" s="1"/>
+      <c r="F106" s="6"/>
+      <c r="G106" s="4"/>
+      <c r="H106" s="1"/>
+      <c r="I106" s="4"/>
+      <c r="J106" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O103" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:O105" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>

--- a/ApiDataBase/AutoGenCode.xlsx
+++ b/ApiDataBase/AutoGenCode.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WorkspaceDDigital\LSM7002MNiosProject\ApiDataBase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F1ADE3-DEE8-400C-BB62-835855C8DB70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631C0106-8D2B-44AD-BD0E-5FE67EC901A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15480" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="bydtatype" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">bydtatype!$A$1:$O$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">bydtatype!$A$1:$O$107</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="272">
   <si>
     <t>SN</t>
   </si>
@@ -912,9 +912,6 @@
     <t>const LMS7002M_dir_t</t>
   </si>
   <si>
-    <t>const short</t>
-  </si>
-  <si>
     <t>const size_t</t>
   </si>
   <si>
@@ -924,9 +921,6 @@
 LMS7002M_LML_BI --&gt;2 
 LMS7002M_LML_BQ --&gt;3
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> const int_arr4 </t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -946,12 +940,6 @@
     <t xml:space="preserve">
 DC offset correction value for Tx TSP chain.
 Correction values are maximum 1.0 (full scale).                                                     Range [-1, 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-DC offset correction value for Tx TSP chain.
-Range [0, 7]                                              windows = 2^(value + 12)
-</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -1055,6 +1043,30 @@
   </si>
   <si>
     <t>Runs TX and RX calibration on the selected channel using the specified bandwidth.</t>
+  </si>
+  <si>
+    <t>CalibrateTx</t>
+  </si>
+  <si>
+    <t>CalibrateRx</t>
+  </si>
+  <si>
+    <t>Runs TX calibration on the selected channel using the specified bandwidth.</t>
+  </si>
+  <si>
+    <t>Runs RX calibration on the selected channel using the specified bandwidth.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+DC offset correction value for Tx TSP chain.
+Range [0, 6]                                              windows = 2^(value + 12)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> const int * </t>
+  </si>
+  <si>
+    <t>const short *</t>
   </si>
 </sst>
 </file>
@@ -1108,7 +1120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1137,9 +1149,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1336,7 +1345,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T106"/>
+  <dimension ref="A1:T108"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" customWidth="1"/>
@@ -1859,7 +1868,7 @@
         <v>225</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -1907,10 +1916,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
@@ -1926,7 +1935,7 @@
         <v>27</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>29</v>
@@ -2726,10 +2735,10 @@
         <v>4</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>246</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>249</v>
       </c>
       <c r="D30" s="1">
         <v>6</v>
@@ -2745,7 +2754,7 @@
         <v>77</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I30" s="4" t="s">
         <v>29</v>
@@ -2778,10 +2787,10 @@
         <v>5</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D31" s="1">
         <v>6</v>
@@ -2797,7 +2806,7 @@
         <v>77</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I31" s="4" t="s">
         <v>29</v>
@@ -2830,10 +2839,10 @@
         <v>6</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D32" s="1">
         <v>6</v>
@@ -2849,7 +2858,7 @@
         <v>77</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I32" s="4" t="s">
         <v>29</v>
@@ -2882,10 +2891,10 @@
         <v>7</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D33" s="1">
         <v>6</v>
@@ -2901,7 +2910,7 @@
         <v>77</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I33" s="4" t="s">
         <v>29</v>
@@ -2934,10 +2943,10 @@
         <v>8</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D34" s="1">
         <v>6</v>
@@ -2953,7 +2962,7 @@
         <v>77</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>29</v>
@@ -3403,7 +3412,7 @@
         <v>103</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D44" s="1">
         <v>8</v>
@@ -3428,7 +3437,7 @@
         <v>73</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>237</v>
+        <v>270</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>22</v>
@@ -3723,7 +3732,7 @@
         <v>124</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D52" s="1">
         <v>12</v>
@@ -3834,10 +3843,10 @@
         <v>180</v>
       </c>
       <c r="M54" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="N54" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="N54" s="1" t="s">
-        <v>235</v>
       </c>
       <c r="O54" s="1" t="s">
         <v>54</v>
@@ -4428,10 +4437,10 @@
         <v>9</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D67" s="1">
         <v>15</v>
@@ -4447,7 +4456,7 @@
         <v>140</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I67" s="4" t="s">
         <v>29</v>
@@ -4775,7 +4784,7 @@
         <v>170</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D75" s="1">
         <v>18</v>
@@ -4827,7 +4836,7 @@
         <v>175</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D76" s="1">
         <v>18</v>
@@ -4879,7 +4888,7 @@
         <v>181</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D77" s="1">
         <v>18</v>
@@ -4959,7 +4968,7 @@
         <v>176</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>241</v>
+        <v>269</v>
       </c>
       <c r="D79" s="1">
         <v>19</v>
@@ -5247,7 +5256,7 @@
         <v>190</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D85" s="1">
         <v>20</v>
@@ -5327,7 +5336,7 @@
         <v>191</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D87" s="1">
         <v>21</v>
@@ -5508,10 +5517,10 @@
         <v>2</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D91" s="1">
         <v>22</v>
@@ -5560,10 +5569,10 @@
         <v>3</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D92" s="1">
         <v>22</v>
@@ -5683,7 +5692,7 @@
         <v>30</v>
       </c>
       <c r="P94" t="str">
-        <f t="shared" ref="P94:P102" si="10">CONCATENATE("typedef ",O94," ",LOWER(F94), "_",  SUBSTITUTE(LOWER(H94), " ", "_"),"(", I94,");")</f>
+        <f t="shared" ref="P94:P101" si="10">CONCATENATE("typedef ",O94," ",LOWER(F94), "_",  SUBSTITUTE(LOWER(H94), " ", "_"),"(", I94,");")</f>
         <v>typedef void trf_rbb_rfe_num_frequency_tunning(LMS7002M_t *);</v>
       </c>
     </row>
@@ -5851,7 +5860,7 @@
         <v>212</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D98" s="1">
         <v>23</v>
@@ -6056,10 +6065,10 @@
         <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D102" s="1">
         <v>23</v>
@@ -6084,13 +6093,13 @@
       <c r="K102" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="L102" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M102" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N102" s="11" t="s">
+      <c r="L102" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M102" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N102" s="1" t="s">
         <v>22</v>
       </c>
       <c r="O102" s="1" t="s">
@@ -6101,59 +6110,79 @@
         <v>typedef void trf_rbb_rfe_num_calibrate(LMS7002M_t *);</v>
       </c>
     </row>
-    <row r="103" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B103" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C103" s="7"/>
-      <c r="D103" s="7"/>
-      <c r="J103" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K103" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L103" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="M103" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="N103" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="O103" s="7"/>
-      <c r="P103" s="7"/>
-      <c r="Q103"/>
-    </row>
-    <row r="104" spans="1:17" ht="51" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A103" s="1">
+        <v>9</v>
+      </c>
+      <c r="B103" t="s">
+        <v>265</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="D103" s="1">
+        <v>23</v>
+      </c>
+      <c r="E103" s="1" t="str">
+        <f t="shared" ref="E103" si="11">DEC2HEX(_xlfn.BITOR(_xlfn.BITLSHIFT(A103,5),D103))</f>
+        <v>137</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="G103" s="4"/>
+      <c r="H103" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="I103" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J103" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M103" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N103" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O103" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P103" t="str">
+        <f>CONCATENATE("typedef ",O103," ",LOWER(F103), "_",  SUBSTITUTE(LOWER(H103), " ", "_"),"(", I103,");")</f>
+        <v>typedef void trf_rbb_rfe_num_calibrate(LMS7002M_t *);</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
-        <v>0</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>219</v>
+        <v>10</v>
+      </c>
+      <c r="B104" t="s">
+        <v>266</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="D104" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E104" s="1" t="str">
-        <f>DEC2HEX(_xlfn.BITOR(_xlfn.BITLSHIFT(A104,5),D104))</f>
-        <v>18</v>
+        <f t="shared" ref="E104" si="12">DEC2HEX(_xlfn.BITOR(_xlfn.BITLSHIFT(A104,5),D104))</f>
+        <v>157</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="G104" s="4" t="s">
-        <v>222</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="G104" s="4"/>
       <c r="H104" s="1" t="s">
-        <v>223</v>
+        <v>173</v>
       </c>
       <c r="I104" s="4" t="s">
         <v>29</v>
@@ -6162,7 +6191,7 @@
         <v>96</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>22</v>
+        <v>174</v>
       </c>
       <c r="L104" s="1" t="s">
         <v>22</v>
@@ -6174,11 +6203,11 @@
         <v>22</v>
       </c>
       <c r="O104" s="1" t="s">
-        <v>224</v>
+        <v>30</v>
       </c>
       <c r="P104" t="str">
         <f>CONCATENATE("typedef ",O104," ",LOWER(F104), "_",  SUBSTITUTE(LOWER(H104), " ", "_"),"(", I104,");")</f>
-        <v>typedef uint16_t readrssi_num_rssi(LMS7002M_t *);</v>
+        <v>typedef void trf_rbb_rfe_num_calibrate(LMS7002M_t *);</v>
       </c>
     </row>
     <row r="105" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -6209,16 +6238,96 @@
       <c r="P105" s="7"/>
       <c r="Q105"/>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="E106" s="1"/>
-      <c r="F106" s="6"/>
-      <c r="G106" s="4"/>
-      <c r="H106" s="1"/>
-      <c r="I106" s="4"/>
-      <c r="J106" s="3"/>
+    <row r="106" spans="1:17" ht="51" x14ac:dyDescent="0.2">
+      <c r="A106" s="1">
+        <v>0</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D106" s="1">
+        <v>24</v>
+      </c>
+      <c r="E106" s="1" t="str">
+        <f>DEC2HEX(_xlfn.BITOR(_xlfn.BITLSHIFT(A106,5),D106))</f>
+        <v>18</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="I106" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J106" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L106" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M106" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N106" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O106" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="P106" t="str">
+        <f>CONCATENATE("typedef ",O106," ",LOWER(F106), "_",  SUBSTITUTE(LOWER(H106), " ", "_"),"(", I106,");")</f>
+        <v>typedef uint16_t readrssi_num_rssi(LMS7002M_t *);</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C107" s="7"/>
+      <c r="D107" s="7"/>
+      <c r="J107" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K107" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L107" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M107" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N107" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="O107" s="7"/>
+      <c r="P107" s="7"/>
+      <c r="Q107"/>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="E108" s="1"/>
+      <c r="F108" s="6"/>
+      <c r="G108" s="4"/>
+      <c r="H108" s="1"/>
+      <c r="I108" s="4"/>
+      <c r="J108" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O105" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:O107" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>
